--- a/OPERA_models_2.9.xlsx
+++ b/OPERA_models_2.9.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mansourik2\Documents\work\OPERA\Modeling\13Prop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mansourik2\Documents\Soft\GitHub\OPERA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7F2FBB-F0F0-4721-AFC7-198F3F53E83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73A91EC-5F5C-402C-9882-F2018BFFE4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24648" yWindow="3204" windowWidth="19416" windowHeight="11892" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -561,10 +561,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -584,9 +582,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -624,7 +622,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -730,7 +728,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -872,7 +870,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -881,17 +879,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.3828125" customWidth="1"/>
-    <col min="4" max="4" width="21.4609375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.23046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.36328125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -904,7 +902,7 @@
       <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" t="s">
@@ -914,248 +912,248 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
       <c r="D3" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>34</v>
       </c>
       <c r="D12" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>37</v>
       </c>
       <c r="D15" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>38</v>
       </c>
       <c r="D16" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>39</v>
       </c>
       <c r="D17" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>40</v>
       </c>
       <c r="D18" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1166,7 @@
       <c r="D19" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="1">
         <v>2.9</v>
       </c>
       <c r="F19" t="s">
@@ -1178,7 +1176,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>44</v>
       </c>
@@ -1188,7 +1186,7 @@
       <c r="D20" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="1">
         <v>2.9</v>
       </c>
       <c r="F20" t="s">
@@ -1198,7 +1196,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>45</v>
       </c>
@@ -1208,7 +1206,7 @@
       <c r="D21" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="1">
         <v>2.6</v>
       </c>
       <c r="F21" t="s">
@@ -1218,7 +1216,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>46</v>
       </c>
@@ -1228,7 +1226,7 @@
       <c r="D22" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="1">
         <v>2.9</v>
       </c>
       <c r="F22" t="s">
@@ -1238,7 +1236,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>47</v>
       </c>
@@ -1248,7 +1246,7 @@
       <c r="D23" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="1">
         <v>2.9</v>
       </c>
       <c r="F23" t="s">
@@ -1258,7 +1256,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>48</v>
       </c>
@@ -1268,7 +1266,7 @@
       <c r="D24" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="1">
         <v>2.9</v>
       </c>
       <c r="F24" t="s">
@@ -1278,7 +1276,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>49</v>
       </c>
@@ -1288,7 +1286,7 @@
       <c r="D25" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="1">
         <v>2.9</v>
       </c>
       <c r="F25" t="s">
@@ -1298,7 +1296,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>50</v>
       </c>
@@ -1308,11 +1306,11 @@
       <c r="D26" t="s">
         <v>79</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>51</v>
       </c>
@@ -1322,11 +1320,11 @@
       <c r="D27" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>52</v>
       </c>
@@ -1336,11 +1334,11 @@
       <c r="D28" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="1">
         <v>2.9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -1353,7 +1351,7 @@
       <c r="D29" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="1">
         <v>2.6</v>
       </c>
       <c r="F29" t="s">
@@ -1363,7 +1361,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>41</v>
       </c>
@@ -1373,7 +1371,7 @@
       <c r="D30" t="s">
         <v>59</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="1">
         <v>2.6</v>
       </c>
       <c r="F30" t="s">
@@ -1383,7 +1381,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>42</v>
       </c>
@@ -1393,7 +1391,7 @@
       <c r="D31" t="s">
         <v>63</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="1">
         <v>2.6</v>
       </c>
       <c r="F31" t="s">
@@ -1403,7 +1401,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>55</v>
       </c>
@@ -1413,7 +1411,7 @@
       <c r="D32" t="s">
         <v>65</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="1">
         <v>2.6</v>
       </c>
       <c r="F32" t="s">
@@ -1423,7 +1421,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>56</v>
       </c>
@@ -1433,7 +1431,7 @@
       <c r="D33" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="1">
         <v>2.6</v>
       </c>
       <c r="F33" t="s">
@@ -1443,7 +1441,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>57</v>
       </c>
@@ -1453,7 +1451,7 @@
       <c r="D34" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="1">
         <v>2.6</v>
       </c>
       <c r="F34" t="s">
@@ -1463,7 +1461,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>93</v>
       </c>
@@ -1476,11 +1474,11 @@
       <c r="D35" t="s">
         <v>65</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>100</v>
       </c>
@@ -1490,11 +1488,11 @@
       <c r="D36" t="s">
         <v>111</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>101</v>
       </c>
@@ -1504,11 +1502,11 @@
       <c r="D37" t="s">
         <v>112</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>102</v>
       </c>
@@ -1518,11 +1516,11 @@
       <c r="D38" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>103</v>
       </c>
@@ -1532,11 +1530,11 @@
       <c r="D39" t="s">
         <v>114</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>104</v>
       </c>
@@ -1546,11 +1544,11 @@
       <c r="D40" t="s">
         <v>115</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>94</v>
       </c>
@@ -1560,11 +1558,11 @@
       <c r="D41" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="3">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E41" s="1">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>95</v>
       </c>
@@ -1574,11 +1572,11 @@
       <c r="D42" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="3">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E42" s="1">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>96</v>
       </c>
@@ -1588,11 +1586,11 @@
       <c r="D43" t="s">
         <v>118</v>
       </c>
-      <c r="E43" s="3">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E43" s="1">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>97</v>
       </c>
@@ -1602,11 +1600,11 @@
       <c r="D44" t="s">
         <v>118</v>
       </c>
-      <c r="E44" s="3">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E44" s="1">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>98</v>
       </c>
@@ -1616,11 +1614,11 @@
       <c r="D45" t="s">
         <v>163</v>
       </c>
-      <c r="E45" s="3">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E45" s="1">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>134</v>
       </c>
@@ -1630,11 +1628,11 @@
       <c r="D46" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>135</v>
       </c>
@@ -1644,108 +1642,108 @@
       <c r="D47" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+        <v>129</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D50" t="s">
-        <v>131</v>
-      </c>
-      <c r="E50" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D51" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>124</v>
+      </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C52" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>124</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E52" s="1">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="C53" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D53" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" s="3">
+        <v>159</v>
+      </c>
+      <c r="E53" s="1">
         <v>2.8</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E54" s="3">
+        <v>165</v>
+      </c>
+      <c r="E54" s="1">
         <v>2.8</v>
       </c>
     </row>
